--- a/storage/app/pdfs/perfiles_descarga.xlsx
+++ b/storage/app/pdfs/perfiles_descarga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains_007 (online tool update)/Entregable/1. Profiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Latinoamerica/6.  Informacion Latam/1. Profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="690" documentId="8_{7FF05819-4066-4415-890C-204B528D78D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D24C117D-6D7A-F645-9AB0-F10D1ABC9B5F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{86CA14A3-0423-6B41-9947-552376DEE6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DB27E61-2420-9449-81E7-D1BA60A2D23B}"/>
   <bookViews>
-    <workbookView xWindow="2980" yWindow="4180" windowWidth="20960" windowHeight="9740" firstSheet="7" activeTab="13" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="3360" yWindow="6300" windowWidth="20960" windowHeight="9740" activeTab="4" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Contenido" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <sheet name="Perú" sheetId="20" r:id="rId16"/>
     <sheet name="Uruguay" sheetId="21" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -754,12 +754,6 @@
     <t>&lt; 0,25 mg/l</t>
   </si>
   <si>
-    <t>Resolución 576/2019</t>
-  </si>
-  <si>
-    <t>Resolución 40103 de 2021</t>
-  </si>
-  <si>
     <t>Gasolina Corriente</t>
   </si>
   <si>
@@ -824,6 +818,12 @@
   </si>
   <si>
     <t>&lt; 3,45 %m/m</t>
+  </si>
+  <si>
+    <t>Resolución576/2019 y Resolución 492/2023</t>
+  </si>
+  <si>
+    <t>Resolución 40444 de 2023</t>
   </si>
 </sst>
 </file>
@@ -1204,14 +1204,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1249,7 +1245,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1355,7 +1351,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1497,7 +1493,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4617,16 +4613,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
@@ -4646,16 +4642,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>39</v>
@@ -4675,16 +4671,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>42</v>
@@ -4868,10 +4864,10 @@
         <v>231</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>63</v>
@@ -5606,7 +5602,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
@@ -6806,16 +6802,16 @@
         <v>20</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>21</v>
@@ -6852,10 +6848,10 @@
         <v>23</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>179</v>
@@ -6875,16 +6871,16 @@
         <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -7359,7 +7355,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -7376,7 +7372,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="30">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -7416,16 +7412,16 @@
         <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="E7" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>238</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -7445,10 +7441,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>112</v>
@@ -7474,7 +7470,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>39</v>
@@ -7648,7 +7644,7 @@
         <v>57</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>126</v>
@@ -7657,7 +7653,7 @@
         <v>116</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -8332,7 +8328,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -8534,16 +8530,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -8592,7 +8588,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>212</v>
@@ -8665,10 +8661,10 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>63</v>

--- a/storage/app/pdfs/perfiles_descarga.xlsx
+++ b/storage/app/pdfs/perfiles_descarga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10724"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Latinoamerica/6.  Informacion Latam/1. Profiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains_007 (online tool update)/Entregable/1. Profiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{86CA14A3-0423-6B41-9947-552376DEE6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DB27E61-2420-9449-81E7-D1BA60A2D23B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{949133B8-7EA7-E44C-B0B5-138C5C400B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="6300" windowWidth="20960" windowHeight="9740" activeTab="4" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="2980" yWindow="4180" windowWidth="20960" windowHeight="9740" firstSheet="7" activeTab="15" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Contenido" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <sheet name="Perú" sheetId="20" r:id="rId16"/>
     <sheet name="Uruguay" sheetId="21" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191028" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="283">
   <si>
     <t>Contenido</t>
   </si>
@@ -240,9 +240,6 @@
     <t>Contenido de oxígeno</t>
   </si>
   <si>
-    <t>&lt; 4.5 %m/m</t>
-  </si>
-  <si>
     <t>&lt;2,7 % m/m</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
   </si>
   <si>
     <t>Etanol (EtOH)</t>
-  </si>
-  <si>
-    <t>&lt;&gt; 12 - 14 %v/v</t>
   </si>
   <si>
     <t>&lt;5 %v/v</t>
@@ -301,15 +295,6 @@
     <t>&lt;22 %v/v</t>
   </si>
   <si>
-    <t>Decreto supremo 2741</t>
-  </si>
-  <si>
-    <t>Resolución 121-18</t>
-  </si>
-  <si>
-    <t>Resolución 042-19</t>
-  </si>
-  <si>
     <t>Todo el país</t>
   </si>
   <si>
@@ -319,18 +304,9 @@
     <t>Gasolina premium</t>
   </si>
   <si>
-    <t>Gasolina para E8</t>
-  </si>
-  <si>
-    <t>Gasolina para E12</t>
-  </si>
-  <si>
     <t>&lt; 3%v/v (2,7%v/v para E12 en verano)</t>
   </si>
   <si>
-    <t>&lt; 42 % v/v</t>
-  </si>
-  <si>
     <t>&lt; 48 %v/v</t>
   </si>
   <si>
@@ -352,9 +328,6 @@
     <t>&lt; 2,7 %m/m</t>
   </si>
   <si>
-    <t>&lt; 8 %v/v</t>
-  </si>
-  <si>
     <t>&lt; 12 %v/v</t>
   </si>
   <si>
@@ -754,6 +727,9 @@
     <t>&lt; 0,25 mg/l</t>
   </si>
   <si>
+    <t>Resolución 40103 de 2021</t>
+  </si>
+  <si>
     <t>Gasolina Corriente</t>
   </si>
   <si>
@@ -820,10 +796,64 @@
     <t>&lt; 3,45 %m/m</t>
   </si>
   <si>
-    <t>Resolución576/2019 y Resolución 492/2023</t>
-  </si>
-  <si>
-    <t>Resolución 40444 de 2023</t>
+    <t>&lt; 5.6 %m/m</t>
+  </si>
+  <si>
+    <t>&lt;&gt; 12 - 15 %v/v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolución 576/2019 y RESOL-2026-79-APN-SE#MEC </t>
+  </si>
+  <si>
+    <t>Decreto supremo 5619 y 5135</t>
+  </si>
+  <si>
+    <t>&lt; 40 % v/v</t>
+  </si>
+  <si>
+    <t>&lt; 10 mg/l</t>
+  </si>
+  <si>
+    <t>&lt; 200 mg/kg</t>
+  </si>
+  <si>
+    <t>&lt; 0.2 %m/m</t>
+  </si>
+  <si>
+    <t>RAR-ANH-DJ-UGJN N.° 0094/2024</t>
+  </si>
+  <si>
+    <t>RAR-ANH-DJ-UGJN N.° 0030/2023</t>
+  </si>
+  <si>
+    <t>RAR-ANH-DJ-UGJN N.° 0404/2024</t>
+  </si>
+  <si>
+    <t>&gt; 99</t>
+  </si>
+  <si>
+    <t>&lt; 2.7 %m/m</t>
+  </si>
+  <si>
+    <t>&lt;&gt; 12-25 %v/v</t>
+  </si>
+  <si>
+    <t>&lt; 93 kPa</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial N.°130/2018</t>
+  </si>
+  <si>
+    <t>Gasolina Regular +</t>
+  </si>
+  <si>
+    <t>Gasolina Super Ethanol 92</t>
+  </si>
+  <si>
+    <t>Gasolina Premium +</t>
+  </si>
+  <si>
+    <t>Gasolina Super Premium 100</t>
   </si>
 </sst>
 </file>
@@ -1073,8 +1103,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1085,8 +1115,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1505,10 +1535,10 @@
     <tabColor rgb="FF002F60"/>
   </sheetPr>
   <dimension ref="A1:A24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="80.84765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
@@ -1525,13 +1555,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="29" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" s="25"/>
+      <c r="A6" s="29"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
@@ -1656,14 +1686,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.89453125" style="6"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -1674,7 +1704,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1684,15 +1714,15 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C4" s="34"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -1702,39 +1732,39 @@
         <v>2022</v>
       </c>
       <c r="C5" s="34"/>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -1754,10 +1784,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -1777,10 +1807,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -1800,10 +1830,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -1823,10 +1853,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -1846,10 +1876,10 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>47</v>
@@ -1869,7 +1899,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
@@ -1926,10 +1956,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -1955,53 +1985,53 @@
         <v>41</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -2009,7 +2039,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -2020,7 +2050,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2031,48 +2061,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2097,14 +2127,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.89453125" style="6"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -2115,7 +2145,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -2125,17 +2155,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -2147,39 +2177,39 @@
       <c r="C5" s="23">
         <v>2021</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -2199,10 +2229,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -2222,10 +2252,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -2245,10 +2275,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -2268,10 +2298,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -2291,10 +2321,10 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>47</v>
@@ -2317,7 +2347,7 @@
         <v>51</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>51</v>
@@ -2371,10 +2401,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -2394,59 +2424,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -2454,7 +2484,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -2465,7 +2495,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2476,48 +2506,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2540,14 +2570,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -2558,7 +2588,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -2568,15 +2598,15 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C4" s="34"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -2586,39 +2616,39 @@
         <v>2017</v>
       </c>
       <c r="C5" s="34"/>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -2638,10 +2668,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -2661,10 +2691,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -2707,10 +2737,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -2730,10 +2760,10 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>47</v>
@@ -2806,10 +2836,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -2829,59 +2859,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -2889,7 +2919,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -2900,7 +2930,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2911,48 +2941,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2977,15 +3007,15 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="38.5" style="12" customWidth="1"/>
-    <col min="8" max="8" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="38.47265625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
@@ -2996,7 +3026,7 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
@@ -3006,19 +3036,19 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="34"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -3032,63 +3062,63 @@
       <c r="E5" s="35"/>
       <c r="F5" s="35"/>
       <c r="G5" s="34"/>
-      <c r="H5" s="29">
+      <c r="H5" s="25">
         <v>2017</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>31</v>
@@ -3108,22 +3138,22 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>36</v>
@@ -3143,22 +3173,22 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>39</v>
@@ -3178,22 +3208,22 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>42</v>
@@ -3248,22 +3278,22 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>47</v>
@@ -3356,22 +3386,22 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>60</v>
@@ -3391,95 +3421,95 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="J17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
@@ -3487,25 +3517,25 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -3514,19 +3544,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
@@ -3537,7 +3567,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -3558,39 +3588,39 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3615,14 +3645,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -3633,7 +3663,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -3643,17 +3673,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -3665,39 +3695,39 @@
       <c r="C5" s="23">
         <v>2021</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -3717,10 +3747,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -3740,10 +3770,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -3763,10 +3793,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -3786,10 +3816,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -3809,10 +3839,10 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>47</v>
@@ -3835,7 +3865,7 @@
         <v>51</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>51</v>
@@ -3889,10 +3919,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -3912,59 +3942,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -3972,7 +4002,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -3983,7 +4013,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -3994,48 +4024,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4058,14 +4088,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -4076,7 +4106,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -4086,57 +4116,57 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C4" s="34"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C5" s="34"/>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -4156,10 +4186,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -4179,10 +4209,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -4202,10 +4232,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -4225,10 +4255,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -4271,7 +4301,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
@@ -4328,10 +4358,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -4351,59 +4381,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -4411,7 +4441,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -4422,7 +4452,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -4433,48 +4463,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4499,14 +4529,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="30.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="30.265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="33.2265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -4517,7 +4547,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -4527,17 +4557,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="34"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -4549,51 +4579,51 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -4613,16 +4643,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
@@ -4642,16 +4672,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>39</v>
@@ -4671,16 +4701,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>42</v>
@@ -4700,16 +4730,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -4729,16 +4759,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -4758,16 +4788,16 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>51</v>
@@ -4829,16 +4859,16 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>60</v>
@@ -4858,73 +4888,73 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -4932,7 +4962,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -4945,7 +4975,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -4958,7 +4988,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -4977,33 +5007,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5028,13 +5058,13 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="42.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="42.5078125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.97265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -5045,7 +5075,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -5055,19 +5085,19 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="33" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E4" s="34"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -5081,51 +5111,51 @@
         <v>2020</v>
       </c>
       <c r="E5" s="34"/>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -5203,10 +5233,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>42</v>
@@ -5232,16 +5262,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -5261,16 +5291,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -5319,10 +5349,10 @@
         <v>53</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>55</v>
@@ -5361,10 +5391,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>60</v>
@@ -5390,73 +5420,73 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -5464,19 +5494,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -5485,7 +5515,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -5498,7 +5528,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -5517,33 +5547,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5570,18 +5600,18 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="6" customWidth="1"/>
-    <col min="6" max="7" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.5" style="12" customWidth="1"/>
-    <col min="11" max="11" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="26.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.29296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6015625" style="6" customWidth="1"/>
+    <col min="6" max="7" width="18.29296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.63671875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="12.5078125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.4453125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="12.5078125" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
@@ -5592,7 +5622,7 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -5601,62 +5631,62 @@
       <c r="A4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29" t="s">
+      <c r="B4" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="25">
         <v>2019</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25">
         <v>2017</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
@@ -5993,95 +6023,95 @@
         <v>61</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="I17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="I18" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="J18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="11" t="s">
+    </row>
+    <row r="19" spans="1:11" s="15" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="B19" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="K18" s="11" t="s">
+      <c r="C19" s="14" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" s="15" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="D19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="G19" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="26" t="s">
         <v>70</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>72</v>
       </c>
       <c r="I19" s="27"/>
       <c r="J19" s="27"/>
@@ -6089,25 +6119,25 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -6116,15 +6146,15 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -6135,72 +6165,72 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="19" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="19" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="H23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="I23" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="J23" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -6227,26 +6257,28 @@
   <sheetPr>
     <tabColor rgb="FFD18316"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="9" customWidth="1"/>
-    <col min="2" max="5" width="32.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="26.09765625" style="9" customWidth="1"/>
+    <col min="2" max="3" width="36.859375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="36.859375" style="12" customWidth="1"/>
+    <col min="6" max="7" width="36.859375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.10546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.44921875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6254,120 +6286,140 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="29" t="s">
+      <c r="B4" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="29">
-        <v>2016</v>
-      </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="16">
+      <c r="B5" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="23">
+        <v>2024</v>
+      </c>
+      <c r="E5" s="23">
         <v>2018</v>
       </c>
-      <c r="E5" s="16">
-        <v>2019</v>
-      </c>
-      <c r="F5" s="29">
+      <c r="F5" s="23">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="23">
+        <v>2024</v>
+      </c>
+      <c r="H5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+      <c r="B6" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="I7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="J7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="K7" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>36</v>
@@ -6375,28 +6427,34 @@
       <c r="I8" s="11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>39</v>
+      <c r="B9" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>39</v>
@@ -6404,27 +6462,33 @@
       <c r="I9" s="11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="E10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="14" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="11" t="s">
@@ -6433,28 +6497,34 @@
       <c r="I10" s="11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>44</v>
+      <c r="B11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>44</v>
@@ -6462,28 +6532,34 @@
       <c r="I11" s="11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>47</v>
+      <c r="B12" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>47</v>
@@ -6491,57 +6567,69 @@
       <c r="I12" s="11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="I13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>56</v>
+      <c r="B14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>55</v>
@@ -6549,41 +6637,49 @@
       <c r="I14" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>60</v>
+      <c r="B16" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>60</v>
@@ -6591,91 +6687,115 @@
       <c r="I16" s="11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="B17" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="J17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="11" t="s">
+      <c r="I18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="21" customFormat="1" ht="56.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="21" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
-        <v>69</v>
-      </c>
       <c r="B19" s="14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+        <v>261</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="28"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6685,10 +6805,12 @@
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6698,66 +6820,73 @@
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="11" t="s">
         <v>41</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="J22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="15" customFormat="1" ht="39" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F19:I19"/>
+  <mergeCells count="8">
+    <mergeCell ref="H19:K19"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="D6:G6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Contenido!A1" display="Contenido" xr:uid="{BD27B5E0-54EA-4ADC-A985-5818923FF284}"/>
@@ -6772,16 +6901,16 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" style="12" customWidth="1"/>
-    <col min="3" max="3" width="27.1640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="23.83203125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="24" style="12" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="6"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.9609375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="27.171875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="23.80859375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="23.9453125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="10.89453125" style="6"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -6792,7 +6921,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -6802,23 +6931,23 @@
         <v>20</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F4" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -6836,51 +6965,51 @@
       <c r="E5" s="16">
         <v>2012</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -6929,16 +7058,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>39</v>
@@ -6958,16 +7087,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>42</v>
@@ -6987,16 +7116,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -7016,16 +7145,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -7074,16 +7203,16 @@
         <v>53</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>55</v>
@@ -7116,16 +7245,16 @@
         <v>58</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>60</v>
@@ -7145,77 +7274,77 @@
         <v>61</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="B19" s="14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -7223,19 +7352,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -7244,7 +7373,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7257,7 +7386,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7276,33 +7405,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -7325,16 +7454,16 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="6"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.8671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.96484375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.89453125" style="6"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -7345,7 +7474,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -7355,73 +7484,73 @@
         <v>20</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
       <c r="E4" s="32"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="30">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="32"/>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -7441,16 +7570,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
@@ -7470,16 +7599,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>39</v>
@@ -7528,16 +7657,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -7586,13 +7715,13 @@
         <v>48</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>50</v>
@@ -7644,16 +7773,16 @@
         <v>57</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -7665,16 +7794,16 @@
         <v>58</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>60</v>
@@ -7696,71 +7825,71 @@
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -7768,7 +7897,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7781,7 +7910,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7794,7 +7923,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7813,33 +7942,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -7864,14 +7993,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.89453125" style="6"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -7882,7 +8011,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -7892,15 +8021,15 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C4" s="34"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -7910,39 +8039,39 @@
         <v>2019</v>
       </c>
       <c r="C5" s="34"/>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -7962,10 +8091,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -7985,10 +8114,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -8008,10 +8137,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -8031,10 +8160,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -8077,7 +8206,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
@@ -8100,7 +8229,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>54</v>
@@ -8134,10 +8263,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -8157,59 +8286,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -8217,7 +8346,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -8228,7 +8357,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -8239,7 +8368,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>41</v>
@@ -8258,25 +8387,25 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -8301,13 +8430,13 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="24.83203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="6"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="24.88671875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="10.89453125" style="6"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -8318,7 +8447,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -8328,17 +8457,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="34"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -8350,51 +8479,51 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -8501,16 +8630,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -8530,16 +8659,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -8559,16 +8688,16 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>51</v>
@@ -8588,13 +8717,13 @@
         <v>53</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>54</v>
@@ -8630,16 +8759,16 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>60</v>
@@ -8661,67 +8790,67 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -8729,7 +8858,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -8742,7 +8871,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -8755,7 +8884,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -8774,33 +8903,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -8825,13 +8954,13 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="25.33203125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="6"/>
-    <col min="7" max="9" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="25.2890625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="10.89453125" style="6"/>
+    <col min="7" max="9" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -8842,7 +8971,7 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -8852,17 +8981,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="34"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -8874,51 +9003,51 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
-      <c r="F5" s="29">
+      <c r="F5" s="25">
         <v>2017</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>31</v>
@@ -8941,13 +9070,13 @@
         <v>36</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
@@ -8967,7 +9096,7 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>39</v>
@@ -8999,13 +9128,13 @@
         <v>42</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>42</v>
@@ -9025,16 +9154,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>44</v>
@@ -9054,16 +9183,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>47</v>
@@ -9146,16 +9275,16 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>60</v>
@@ -9175,69 +9304,69 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
@@ -9245,7 +9374,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -9258,7 +9387,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -9271,7 +9400,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -9290,33 +9419,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
       <c r="A23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -9341,14 +9470,14 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="7" width="12.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="27.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.47265625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.89453125" style="6"/>
+    <col min="5" max="7" width="12.5078125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.89453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
@@ -9359,7 +9488,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -9369,17 +9498,17 @@
         <v>20</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
@@ -9391,39 +9520,39 @@
       <c r="C5" s="23">
         <v>2021</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>2017</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>31</v>
@@ -9443,10 +9572,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>36</v>
@@ -9466,10 +9595,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>39</v>
@@ -9489,10 +9618,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>42</v>
@@ -9512,10 +9641,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>44</v>
@@ -9535,10 +9664,10 @@
         <v>45</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>47</v>
@@ -9558,7 +9687,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>51</v>
@@ -9615,10 +9744,10 @@
         <v>58</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>60</v>
@@ -9638,59 +9767,59 @@
         <v>61</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>64</v>
-      </c>
       <c r="F17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
@@ -9698,7 +9827,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -9709,7 +9838,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -9720,48 +9849,48 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="15" customFormat="1" ht="51" x14ac:dyDescent="0.15">
+      <c r="A23" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
